--- a/results/02_taxa_assemblage/Wards_LDA/cluster_classifier/tables/mccv_classification_report.xlsx
+++ b/results/02_taxa_assemblage/Wards_LDA/cluster_classifier/tables/mccv_classification_report.xlsx
@@ -458,17 +458,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.677 ± 0.227</t>
+          <t>0.660 ± 0.238</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.723 ± 0.229</t>
+          <t>0.661 ± 0.256</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.670 ± 0.180</t>
+          <t>0.632 ± 0.201</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -483,21 +483,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.530 ± 0.130</t>
+          <t>0.607 ± 0.184</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.645 ± 0.225</t>
+          <t>0.634 ± 0.245</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.570 ± 0.153</t>
+          <t>0.600 ± 0.183</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -508,21 +508,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.197 ± 0.250</t>
+          <t>0.147 ± 0.213</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.145 ± 0.173</t>
+          <t>0.150 ± 0.200</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.158 ± 0.181</t>
+          <t>0.142 ± 0.186</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -540,21 +540,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.455 ± 0.130</t>
+          <t>0.485 ± 0.127</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.498 ± 0.113</t>
+          <t>0.497 ± 0.131</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.458 ± 0.108</t>
+          <t>0.472 ± 0.119</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -574,7 +574,7 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.498 ± 0.113</t>
+          <t>0.497 ± 0.131</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>

--- a/results/02_taxa_assemblage/Wards_LDA/cluster_classifier/tables/mccv_classification_report.xlsx
+++ b/results/02_taxa_assemblage/Wards_LDA/cluster_classifier/tables/mccv_classification_report.xlsx
@@ -458,17 +458,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.660 ± 0.238</t>
+          <t>0.709 ± 0.231</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.661 ± 0.256</t>
+          <t>0.703 ± 0.243</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.632 ± 0.201</t>
+          <t>0.674 ± 0.187</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -483,17 +483,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.607 ± 0.184</t>
+          <t>0.494 ± 0.144</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.634 ± 0.245</t>
+          <t>0.662 ± 0.247</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.600 ± 0.183</t>
+          <t>0.554 ± 0.166</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -508,21 +508,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.147 ± 0.213</t>
+          <t>0.208 ± 0.264</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.150 ± 0.200</t>
+          <t>0.151 ± 0.177</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.142 ± 0.186</t>
+          <t>0.165 ± 0.186</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -540,21 +540,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.485 ± 0.127</t>
+          <t>0.448 ± 0.146</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.497 ± 0.131</t>
+          <t>0.488 ± 0.119</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.472 ± 0.119</t>
+          <t>0.445 ± 0.114</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
@@ -574,7 +574,7 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.497 ± 0.131</t>
+          <t>0.488 ± 0.119</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -589,7 +589,7 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.5000</t>
+          <t>0.4545</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>

--- a/results/02_taxa_assemblage/Wards_LDA/cluster_classifier/tables/mccv_classification_report.xlsx
+++ b/results/02_taxa_assemblage/Wards_LDA/cluster_classifier/tables/mccv_classification_report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,17 +458,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.709 ± 0.231</t>
+          <t>0.648 ± 0.316</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.703 ± 0.243</t>
+          <t>0.501 ± 0.270</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.674 ± 0.187</t>
+          <t>0.532 ± 0.241</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -483,135 +483,110 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.494 ± 0.144</t>
+          <t>0.746 ± 0.121</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.662 ± 0.247</t>
+          <t>0.824 ± 0.174</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.554 ± 0.166</t>
+          <t>0.771 ± 0.116</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Cluster 3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>0.208 ± 0.264</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>0.151 ± 0.177</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0.165 ± 0.186</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>4</v>
-      </c>
+      <c r="A4" s="1" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Weighted Avg</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0.709 ± 0.173</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0.703 ± 0.135</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.682 ± 0.147</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Weighted Avg</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>0.448 ± 0.146</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0.488 ± 0.119</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>0.445 ± 0.114</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>11</v>
-      </c>
+      <c r="A6" s="1" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr"/>
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Mean accuracy</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0.703 ± 0.135</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Mean accuracy</t>
+          <t>Median accuracy</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.488 ± 0.119</t>
+          <t>0.7500</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>Median accuracy</t>
-        </is>
-      </c>
+      <c r="A9" s="1" t="inlineStr"/>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>0.4545</t>
-        </is>
-      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr"/>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Note: Metrics shown as mean ± std across 1,000 CV iterations</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>Note: Metrics shown as mean ± std across 1,000 CV iterations</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
